--- a/Numerai_data_staking_sumarry.xlsx
+++ b/Numerai_data_staking_sumarry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moda2\Documents\moda\Holdings-of-Numerai-GP-LLC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moda2\Projects\Holdings-of-Numerai-GP-LLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D268AE-ED9A-4F48-A0E6-7E434A6074BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD279BB-CCBD-4F75-A65D-6FD44B02E7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{1266EB20-D47D-4DF9-B6B0-D9F656D8C5C3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{1266EB20-D47D-4DF9-B6B0-D9F656D8C5C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Change History" sheetId="2" r:id="rId1"/>
